--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>掉落id</t>
   </si>
@@ -50,37 +50,7 @@
     <t>研究点01</t>
   </si>
   <si>
-    <t>500_1024005_0|500_1024005_1</t>
-  </si>
-  <si>
-    <t>研究点02</t>
-  </si>
-  <si>
-    <t>500_1024005_2|500_1024005_4</t>
-  </si>
-  <si>
-    <t>研究点03</t>
-  </si>
-  <si>
-    <t>500_1024005_5|500_1024005_10</t>
-  </si>
-  <si>
-    <t>筹码01</t>
-  </si>
-  <si>
-    <t>500_1024004_1</t>
-  </si>
-  <si>
-    <t>筹码02</t>
-  </si>
-  <si>
-    <t>500_1024004_5</t>
-  </si>
-  <si>
-    <t>筹码03</t>
-  </si>
-  <si>
-    <t>500_1024004_10</t>
+    <t>500_1024005_1|250_1024005_2</t>
   </si>
 </sst>
 </file>
@@ -1234,8 +1204,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
@@ -1280,61 +1250,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:3">
-      <c r="A5" s="1">
-        <v>10000002</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:3">
-      <c r="A6" s="1">
-        <v>10000003</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:3">
-      <c r="A7" s="1">
-        <v>20000001</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:3">
-      <c r="A8" s="1">
-        <v>20000002</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:3">
-      <c r="A9" s="1">
-        <v>20000003</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -1204,8 +1204,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
@@ -1240,13 +1240,18 @@
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
-      <c r="A4" s="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:3">
+      <c r="A5" s="1">
         <v>10000001</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>掉落id</t>
   </si>
@@ -47,10 +47,70 @@
     <t>detailedDropItem</t>
   </si>
   <si>
-    <t>研究点01</t>
+    <t>普通研究点</t>
   </si>
   <si>
     <t>500_1024005_1|250_1024005_2</t>
+  </si>
+  <si>
+    <t>超级明星专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024024_1|250_1024024_2</t>
+  </si>
+  <si>
+    <t>神马飞扬专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024025_1|250_1024025_2</t>
+  </si>
+  <si>
+    <t>虎虎生财专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024026_1|250_1024026_2</t>
+  </si>
+  <si>
+    <t>埃及艳后专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024027_1|250_1024027_2</t>
+  </si>
+  <si>
+    <t>金蛇招财专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024028_1|250_1024028_2</t>
+  </si>
+  <si>
+    <t>金钱兔专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024029_1|250_1024029_2</t>
+  </si>
+  <si>
+    <t>麻将胡了专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024030_1|250_1024030_2</t>
+  </si>
+  <si>
+    <t>牛气冲天专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024031_1|250_1024031_2</t>
+  </si>
+  <si>
+    <t>鼠鼠福福专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024032_1|250_1024032_2</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024033_1|250_1024033_2</t>
   </si>
 </sst>
 </file>
@@ -672,11 +732,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,55 +1270,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="3" width="22.875" customWidth="1"/>
+    <col min="1" max="1" width="17" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
     </row>
-    <row r="5" ht="16.5" spans="1:3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
         <v>10000001</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2">
+        <v>10000007</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2">
+        <v>10000008</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2">
+        <v>10000009</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2">
+        <v>10000010</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2">
+        <v>10000011</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>掉落id</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>500_1024033_1|250_1024033_2</t>
+  </si>
+  <si>
+    <t>财神专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024040_1|250_1024040_2</t>
   </si>
 </sst>
 </file>
@@ -732,7 +738,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,9 +746,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1270,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1326,7 +1329,7 @@
       <c r="A6" s="2">
         <v>10000002</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1430,6 +1433,17 @@
       </c>
       <c r="C15" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2">
+        <v>10000012</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>掉落id</t>
   </si>
@@ -117,6 +117,48 @@
   </si>
   <si>
     <t>500_1024040_1|250_1024040_2</t>
+  </si>
+  <si>
+    <t>篮球巨星专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024076_1|250_1024076_2</t>
+  </si>
+  <si>
+    <t>寒冰王座专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024077_1|250_1024077_2</t>
+  </si>
+  <si>
+    <t>绿巨人专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024078_1|250_1024078_2</t>
+  </si>
+  <si>
+    <t>雷神专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024079_1|250_1024079_2</t>
+  </si>
+  <si>
+    <t>杰克船长专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024080_1|250_1024080_2</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024081_1|250_1024081_2</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024082_1|250_1024082_2</t>
   </si>
 </sst>
 </file>
@@ -129,7 +171,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +186,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -482,12 +530,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -608,137 +671,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -746,6 +809,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1273,7 +1339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1446,6 +1512,83 @@
         <v>29</v>
       </c>
     </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2">
+        <v>10000013</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2">
+        <v>10000014</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2">
+        <v>10000015</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2">
+        <v>10000016</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2">
+        <v>10000017</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2">
+        <v>10000018</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2">
+        <v>10000019</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>掉落id</t>
   </si>
@@ -159,6 +164,18 @@
   </si>
   <si>
     <t>500_1024082_1|250_1024082_2</t>
+  </si>
+  <si>
+    <t>象财神专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024083_1|250_1024083_2</t>
+  </si>
+  <si>
+    <t>狼月专属研究点</t>
+  </si>
+  <si>
+    <t>500_1024084_1|250_1024084_2</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1589,6 +1606,28 @@
         <v>43</v>
       </c>
     </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2">
+        <v>10000020</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2">
+        <v>10000021</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -55,7 +55,7 @@
     <t>普通研究点</t>
   </si>
   <si>
-    <t>500_1024005_1|250_1024005_2</t>
+    <t>500_1024005_2|250_1024005_4|100_1024005_6</t>
   </si>
   <si>
     <t>超级明星专属研究点</t>

--- a/hall/resources/sample/dropNum.xlsx
+++ b/hall/resources/sample/dropNum.xlsx
@@ -55,127 +55,127 @@
     <t>普通研究点</t>
   </si>
   <si>
-    <t>500_1024005_2|250_1024005_4|100_1024005_6</t>
+    <t>500_1024005_10|250_1024005_20|100_1024005_30</t>
   </si>
   <si>
     <t>超级明星专属研究点</t>
   </si>
   <si>
-    <t>500_1024024_1|250_1024024_2</t>
+    <t>500_1024024_10|250_1024024_20</t>
   </si>
   <si>
     <t>神马飞扬专属研究点</t>
   </si>
   <si>
-    <t>500_1024025_1|250_1024025_2</t>
+    <t>500_1024025_10|250_1024025_20</t>
   </si>
   <si>
     <t>虎虎生财专属研究点</t>
   </si>
   <si>
-    <t>500_1024026_1|250_1024026_2</t>
+    <t>500_1024026_10|250_1024026_20</t>
   </si>
   <si>
     <t>埃及艳后专属研究点</t>
   </si>
   <si>
-    <t>500_1024027_1|250_1024027_2</t>
+    <t>500_1024027_10|250_1024027_20</t>
   </si>
   <si>
     <t>金蛇招财专属研究点</t>
   </si>
   <si>
-    <t>500_1024028_1|250_1024028_2</t>
+    <t>500_1024028_10|250_1024028_20</t>
   </si>
   <si>
     <t>金钱兔专属研究点</t>
   </si>
   <si>
-    <t>500_1024029_1|250_1024029_2</t>
+    <t>500_1024029_10|250_1024029_20</t>
   </si>
   <si>
     <t>麻将胡了专属研究点</t>
   </si>
   <si>
-    <t>500_1024030_1|250_1024030_2</t>
+    <t>500_1024030_10|250_1024030_20</t>
   </si>
   <si>
     <t>牛气冲天专属研究点</t>
   </si>
   <si>
-    <t>500_1024031_1|250_1024031_2</t>
+    <t>500_1024031_10|250_1024031_20</t>
   </si>
   <si>
     <t>鼠鼠福福专属研究点</t>
   </si>
   <si>
-    <t>500_1024032_1|250_1024032_2</t>
+    <t>500_1024032_10|250_1024032_20</t>
   </si>
   <si>
     <t>圣诞狂欢夜专属研究点</t>
   </si>
   <si>
-    <t>500_1024033_1|250_1024033_2</t>
+    <t>500_1024033_10|250_1024033_20</t>
   </si>
   <si>
     <t>财神专属研究点</t>
   </si>
   <si>
-    <t>500_1024040_1|250_1024040_2</t>
+    <t>500_1024040_10|250_1024040_20</t>
   </si>
   <si>
     <t>篮球巨星专属研究点</t>
   </si>
   <si>
-    <t>500_1024076_1|250_1024076_2</t>
+    <t>500_1024076_10|250_1024076_20</t>
   </si>
   <si>
     <t>寒冰王座专属研究点</t>
   </si>
   <si>
-    <t>500_1024077_1|250_1024077_2</t>
+    <t>500_1024077_10|250_1024077_20</t>
   </si>
   <si>
     <t>绿巨人专属研究点</t>
   </si>
   <si>
-    <t>500_1024078_1|250_1024078_2</t>
+    <t>500_1024078_10|250_1024078_20</t>
   </si>
   <si>
     <t>雷神专属研究点</t>
   </si>
   <si>
-    <t>500_1024079_1|250_1024079_2</t>
+    <t>500_1024079_10|250_1024079_20</t>
   </si>
   <si>
     <t>杰克船长专属研究点</t>
   </si>
   <si>
-    <t>500_1024080_1|250_1024080_2</t>
+    <t>500_1024080_10|250_1024080_20</t>
   </si>
   <si>
     <t>愤怒的小鸟专属研究点</t>
   </si>
   <si>
-    <t>500_1024081_1|250_1024081_2</t>
+    <t>500_1024081_10|250_1024081_20</t>
   </si>
   <si>
     <t>宙斯vs哈迪斯专属研究点</t>
   </si>
   <si>
-    <t>500_1024082_1|250_1024082_2</t>
+    <t>500_1024082_10|250_1024082_20</t>
   </si>
   <si>
     <t>象财神专属研究点</t>
   </si>
   <si>
-    <t>500_1024083_1|250_1024083_2</t>
+    <t>500_1024083_10|250_1024083_20</t>
   </si>
   <si>
     <t>狼月专属研究点</t>
   </si>
   <si>
-    <t>500_1024084_1|250_1024084_2</t>
+    <t>500_1024084_10|250_1024084_20</t>
   </si>
 </sst>
 </file>
